--- a/doc/텔레그램 메세지 로직.xlsx
+++ b/doc/텔레그램 메세지 로직.xlsx
@@ -7,16 +7,16 @@
     <workbookView xWindow="360" yWindow="45" windowWidth="28035" windowHeight="12570"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="추천물건전달메세지" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="텔레그램메세지현황" sheetId="1" r:id="rId1"/>
+    <sheet name="추천물건전달메세지" sheetId="4" r:id="rId2"/>
+    <sheet name="입찰취소전달메세지" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="63">
   <si>
     <t>추천물건전달</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -42,31 +42,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>입찰취소전달</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>관리자 텔레그램 [입찰가 안내] 선택 전송</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>입찰불가안내</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>회원 [입찰취소] 선택 전송</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>관리자 텔레그램 [입찰불가 안내] 선택 전송</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>입찰가확인</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>현재 물건상태 변경이 불가능 합니다.(현재 상태: 입찰)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -94,15 +74,112 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>현재 물건상태 변경이 불가능 합니다.(현재 상태: 미정)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>입찰취소는 MAPS의 물건상태가 입찰일때만 가능</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>입찰취소는 MAPS의 물건상태가 추천 일때만 가능</t>
+    <t>입찰확정 선택 후 자동 메시지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>텔레그램 [추천물건안내] 선택 전송</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>물건상태가 추천일경우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>물건상태가 추천이 아닐경우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조건</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메시지 내용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[추천물건전달메세지] 시트 참조</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>행위</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입찰취소 선택 후 자동 메시지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>물건상태가 입찰일경우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제목</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>행위자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>텔레그램 [입찰가안내] 선택 전송</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입찰가 확인 버튼 선택</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입찰확정 버튼 선택</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>입찰취소 버튼 선택</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>텔레그램 [입찰불가안내] 선택 전송</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>물건상태가 추천, 입찰 일경우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>물건상태가 입찰일 경우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MJMAPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MJ 경매 스쿨입니다. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">추천물건 전달드립니다. </t>
+  </si>
+  <si>
+    <t>48시간 이내 입찰확정 부탁드리며, 이후 자동 취소 됩니다.</t>
+  </si>
+  <si>
+    <t>🔴 물건상태: 추천</t>
+  </si>
+  <si>
+    <t>서울/수도권(경기,인천) 입찰하시는 분은 1주택자만 대출이가능합니다!!</t>
+  </si>
+  <si>
+    <t>1. 입찰가 관리: 이정우: (010-4238-7781)</t>
+  </si>
+  <si>
+    <t>2. 단기투자클럽 관리: 이경미님 (010-3448-8035)</t>
+  </si>
+  <si>
+    <t>현재 물건상태 변경이 불가능 합니다.(현재 상태: "stu_member")</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26-03-21 / TEST6 / 공매
+입찰가가 도착했습니다. 확인하시겠습니까?</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -113,83 +190,91 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>입찰확정 선택 후 자동 메시지</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>텔레그램 [추천물건안내] 선택 전송</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>물건상태가 추천일경우</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>물건상태가 추천이 아닐경우</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>조건</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>메시지 내용</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[추천물건전달메세지] 시트 참조</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>행위</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>입찰취소 선택 후 자동 메시지</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>물건상태가 입찰일경우</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>제목</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>행위자</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>텔레그램 [입찰가안내] 선택 전송</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>입찰가 확인 버튼 선택</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>입찰확정 버튼 선택</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>입찰취소 버튼 선택</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>텔레그램 [입찰불가안내] 선택 전송</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>물건상태가 추천, 입찰 일경우</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>물건상태가 입찰일 경우</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
+    <t>물건상태가 변경일 경우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MJ 경매 스쿨입니다. 입찰불가 안내 드립니다.</t>
+  </si>
+  <si>
+    <t>해당 물건은 입찰이 취소 되었습니다.</t>
+  </si>
+  <si>
+    <t>🔴 물건상태: 입찰</t>
+  </si>
+  <si>
+    <t>📅 입찰일자: 2026-03-21</t>
+  </si>
+  <si>
+    <t>📄 사건번호: TEST6</t>
+  </si>
+  <si>
+    <t>🏛️ 법원: 공매</t>
+  </si>
+  <si>
+    <t>👤 회원: 이정우</t>
+  </si>
+  <si>
+    <r>
+      <t>👨</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>‍</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>💼 담당: 대표님</t>
+    </r>
+  </si>
+  <si>
+    <t>💰 입찰가: 330,000,000,000원</t>
+  </si>
+  <si>
+    <t>3. 돈클</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - 1. 돈버는클래스 오픈채팅방 MJ스태프 1:1 카톡</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - 2. 돈버는클래스 담당: 김재휘님 (010-3448-8035)</t>
+  </si>
+  <si>
+    <t>📅 입찰일자: 2026-03-29</t>
+  </si>
+  <si>
+    <t>📄 사건번호: T1234</t>
+  </si>
+  <si>
+    <t>🏛️ 법원: 인천</t>
+  </si>
+  <si>
+    <t>[입찰취소전달메세지] 시트 참조</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>순번</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>물건상태가 입찰이 아닐 경우</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>* 회원 화면에서 입찰가는 물건상태가 입찰일 때만 확인가능</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -197,7 +282,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -222,6 +307,13 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -243,7 +335,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -266,13 +358,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -303,8 +408,14 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -607,257 +718,261 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C2:H24"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="9" style="1"/>
-    <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="38.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="32" customWidth="1"/>
-    <col min="7" max="7" width="53.875" customWidth="1"/>
-    <col min="8" max="8" width="46.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9" style="1"/>
+    <col min="3" max="3" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="32" customWidth="1"/>
+    <col min="6" max="6" width="51.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:8" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C2" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E2" s="7" t="s">
+    <row r="1" spans="1:6" s="1" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="9">
+        <v>1</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="49.5" x14ac:dyDescent="0.3">
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="33" x14ac:dyDescent="0.3">
+      <c r="A9" s="9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="66" x14ac:dyDescent="0.3">
+      <c r="A10" s="4">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="9">
+        <v>10</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="3:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="H3" s="10"/>
-    </row>
-    <row r="4" spans="3:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="3:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="4"/>
-    </row>
-    <row r="6" spans="3:8" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="C6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6" s="3"/>
-    </row>
-    <row r="7" spans="3:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="3:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" s="4"/>
-    </row>
-    <row r="9" spans="3:8" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="C9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" s="3"/>
-    </row>
-    <row r="10" spans="3:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C10" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H10" s="3"/>
-    </row>
-    <row r="11" spans="3:8" ht="66" x14ac:dyDescent="0.3">
-      <c r="C11" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H11" s="3"/>
-    </row>
-    <row r="12" spans="3:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C12" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H12" s="3"/>
-    </row>
-    <row r="13" spans="3:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H13" s="3"/>
-    </row>
-    <row r="14" spans="3:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="3:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="3:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="17" spans="5:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E17" s="8"/>
-    </row>
-    <row r="18" spans="5:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E18" s="8"/>
-    </row>
-    <row r="19" spans="5:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E19" s="8"/>
-    </row>
-    <row r="20" spans="5:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="21" spans="5:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="22" spans="5:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="23" spans="5:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="24" spans="5:5" ht="22.5" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="E11" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="12" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="12"/>
+    </row>
+    <row r="15" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D15" s="8"/>
+    </row>
+    <row r="16" spans="1:6" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D16" s="8"/>
+    </row>
+    <row r="17" spans="4:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D17" s="8"/>
+    </row>
+    <row r="18" spans="4:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="4:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="4:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="4:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="4:4" ht="22.5" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="H4:H5"/>
-  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -866,9 +981,95 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -876,9 +1077,95 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
